--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N62_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N62_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.09817537752685</v>
+        <v>5.378453498848113</v>
       </c>
       <c r="D2" t="n">
-        <v>67.44385245491004</v>
+        <v>10.95962602392288</v>
       </c>
       <c r="E2" t="n">
-        <v>13.88058657542886</v>
+        <v>2.25559531850719</v>
       </c>
       <c r="F2" t="n">
-        <v>21.14242737919018</v>
+        <v>3.435644449118405</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.27802468263601</v>
+        <v>4.107679010928352</v>
       </c>
       <c r="D3" t="n">
-        <v>25.04239036499399</v>
+        <v>4.069388434311524</v>
       </c>
       <c r="E3" t="n">
-        <v>13.88058657542886</v>
+        <v>2.25559531850719</v>
       </c>
       <c r="F3" t="n">
-        <v>21.14242737919018</v>
+        <v>3.435644449118405</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>62.1274547774099</v>
+        <v>10.09571140132911</v>
       </c>
       <c r="D4" t="n">
-        <v>21.94168977259834</v>
+        <v>3.56552458804723</v>
       </c>
       <c r="E4" t="n">
-        <v>13.88058657542886</v>
+        <v>2.25559531850719</v>
       </c>
       <c r="F4" t="n">
-        <v>21.14242737919018</v>
+        <v>3.435644449118405</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>53.40395539649928</v>
+        <v>8.678142751931134</v>
       </c>
       <c r="D5" t="n">
-        <v>11.3861271039728</v>
+        <v>1.850245654395579</v>
       </c>
       <c r="E5" t="n">
-        <v>13.88058657542886</v>
+        <v>2.25559531850719</v>
       </c>
       <c r="F5" t="n">
-        <v>21.14242737919018</v>
+        <v>3.435644449118405</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>57.89219617554067</v>
+        <v>9.40748187852536</v>
       </c>
       <c r="D6" t="n">
-        <v>7.887104665278014</v>
+        <v>1.281654508107677</v>
       </c>
       <c r="E6" t="n">
-        <v>13.88058657542886</v>
+        <v>2.25559531850719</v>
       </c>
       <c r="F6" t="n">
-        <v>21.14242737919018</v>
+        <v>3.435644449118405</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>57.55693980612156</v>
+        <v>9.353002718494754</v>
       </c>
       <c r="D7" t="n">
-        <v>4.609772228646444</v>
+        <v>0.7490879871550471</v>
       </c>
       <c r="E7" t="n">
-        <v>13.88058657542886</v>
+        <v>2.25559531850719</v>
       </c>
       <c r="F7" t="n">
-        <v>21.14242737919018</v>
+        <v>3.435644449118405</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
